--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD734F7-7917-4AD5-B2D9-CECF9C671E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A68D58-7102-4011-9C0A-C512B0B949EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -126,9 +126,6 @@
     <t>Cristina Gragera</t>
   </si>
   <si>
-    <t>Álvaro Monleon</t>
-  </si>
-  <si>
     <t>Jorge García</t>
   </si>
   <si>
@@ -151,6 +148,9 @@
   </si>
   <si>
     <t>Paula Torres</t>
+  </si>
+  <si>
+    <t>Álvaro Monleón</t>
   </si>
 </sst>
 </file>
@@ -953,7 +953,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -977,7 +977,7 @@
         <v>14</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>18</v>
@@ -1004,10 +1004,10 @@
         <v>15</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -1112,10 +1112,10 @@
         <v>19</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -1139,10 +1139,10 @@
         <v>20</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -1220,7 +1220,7 @@
         <v>24</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>28</v>
@@ -1331,7 +1331,7 @@
         <v>30</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -1466,7 +1466,7 @@
         <v>31</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1547,7 +1547,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
@@ -1571,7 +1571,7 @@
         <v>40</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>21</v>
@@ -1598,7 +1598,7 @@
         <v>41</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>32</v>
@@ -1652,7 +1652,7 @@
         <v>45</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>18</v>
@@ -1679,7 +1679,7 @@
         <v>46</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>29</v>
@@ -1760,7 +1760,7 @@
         <v>50</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>27</v>
@@ -1841,7 +1841,7 @@
         <v>53</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>2</v>
@@ -1976,10 +1976,10 @@
         <v>58</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -2003,7 +2003,7 @@
         <v>59</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>29</v>
@@ -2084,7 +2084,7 @@
         <v>63</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>21</v>
@@ -2165,10 +2165,10 @@
         <v>69</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
@@ -2246,7 +2246,7 @@
         <v>72</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>17</v>
@@ -2273,7 +2273,7 @@
         <v>73</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>31</v>
@@ -2489,7 +2489,7 @@
         <v>84</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>30</v>
@@ -2597,10 +2597,10 @@
         <v>89</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
@@ -2678,7 +2678,7 @@
         <v>93</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>25</v>
@@ -2708,7 +2708,7 @@
         <v>18</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
@@ -2732,7 +2732,7 @@
         <v>95</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>31</v>
@@ -2813,10 +2813,10 @@
         <v>100</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -2921,7 +2921,7 @@
         <v>104</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>28</v>
@@ -3002,7 +3002,7 @@
         <v>108</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>30</v>
@@ -3086,7 +3086,7 @@
         <v>32</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
@@ -3164,7 +3164,7 @@
         <v>116</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>29</v>
@@ -3275,7 +3275,7 @@
         <v>21</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
@@ -3326,7 +3326,7 @@
         <v>125</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>27</v>
@@ -3353,10 +3353,10 @@
         <v>126</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
@@ -3542,10 +3542,10 @@
         <v>134</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
@@ -3599,7 +3599,7 @@
         <v>13</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
@@ -3650,10 +3650,10 @@
         <v>139</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
@@ -3758,10 +3758,10 @@
         <v>143</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
@@ -3920,7 +3920,7 @@
         <v>152</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>32</v>
@@ -4058,7 +4058,7 @@
         <v>23</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F125" s="4"/>
       <c r="G125" s="4"/>
@@ -4163,7 +4163,7 @@
         <v>163</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>28</v>
@@ -4190,7 +4190,7 @@
         <v>164</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>32</v>
@@ -4298,7 +4298,7 @@
         <v>168</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>18</v>
@@ -4328,7 +4328,7 @@
         <v>31</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
@@ -4409,7 +4409,7 @@
         <v>30</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
@@ -4433,7 +4433,7 @@
         <v>174</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>29</v>
@@ -4487,7 +4487,7 @@
         <v>178</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>27</v>
@@ -4568,7 +4568,7 @@
         <v>183</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>28</v>
@@ -4625,7 +4625,7 @@
         <v>26</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F146" s="1"/>
       <c r="G146" s="1"/>
@@ -4649,7 +4649,7 @@
         <v>187</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>21</v>
@@ -4838,10 +4838,10 @@
         <v>195</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
@@ -4919,7 +4919,7 @@
         <v>199</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>27</v>

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117D1459-1A26-4447-A8EE-B075D0C2D98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C55B7B-5EF0-45C6-930E-79C5BCD84183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -361,7 +361,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -412,35 +412,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bueno" xfId="1" builtinId="26"/>
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -756,8 +734,8 @@
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5546875" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
     <col min="6" max="15" width="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -861,12 +839,24 @@
       <c r="E3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="F3" s="3">
+        <v>5</v>
+      </c>
+      <c r="G3" s="3">
+        <v>11</v>
+      </c>
+      <c r="H3" s="3">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3">
+        <v>13</v>
+      </c>
+      <c r="J3" s="3">
+        <v>6</v>
+      </c>
+      <c r="K3" s="3">
+        <v>11</v>
+      </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -984,12 +974,24 @@
       <c r="E7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="F7" s="3">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3">
+        <v>11</v>
+      </c>
+      <c r="H7" s="3">
+        <v>8</v>
+      </c>
+      <c r="I7" s="3">
+        <v>11</v>
+      </c>
+      <c r="J7" s="3">
+        <v>10</v>
+      </c>
+      <c r="K7" s="3">
+        <v>12</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -1012,10 +1014,18 @@
       <c r="E8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="F8" s="4">
+        <v>5</v>
+      </c>
+      <c r="G8" s="4">
+        <v>11</v>
+      </c>
+      <c r="H8" s="4">
+        <v>5</v>
+      </c>
+      <c r="I8" s="4">
+        <v>11</v>
+      </c>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -1040,10 +1050,18 @@
       <c r="E9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="F9" s="2">
+        <v>11</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3</v>
+      </c>
+      <c r="H9" s="2">
+        <v>11</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C55B7B-5EF0-45C6-930E-79C5BCD84183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DBC7C4-0266-4487-B607-8FC949F8C698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -879,10 +879,18 @@
       <c r="E4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="F4" s="4">
+        <v>7</v>
+      </c>
+      <c r="G4" s="4">
+        <v>11</v>
+      </c>
+      <c r="H4" s="4">
+        <v>7</v>
+      </c>
+      <c r="I4" s="4">
+        <v>11</v>
+      </c>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
@@ -946,14 +954,30 @@
       <c r="E6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="F6" s="1">
+        <v>9</v>
+      </c>
+      <c r="G6" s="1">
+        <v>11</v>
+      </c>
+      <c r="H6" s="1">
+        <v>5</v>
+      </c>
+      <c r="I6" s="1">
+        <v>11</v>
+      </c>
+      <c r="J6" s="1">
+        <v>11</v>
+      </c>
+      <c r="K6" s="1">
+        <v>7</v>
+      </c>
+      <c r="L6" s="1">
+        <v>9</v>
+      </c>
+      <c r="M6" s="1">
+        <v>11</v>
+      </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -1085,14 +1109,30 @@
       <c r="E10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
+      <c r="F10" s="1">
+        <v>6</v>
+      </c>
+      <c r="G10" s="1">
+        <v>11</v>
+      </c>
+      <c r="H10" s="1">
+        <v>11</v>
+      </c>
+      <c r="I10" s="1">
+        <v>9</v>
+      </c>
+      <c r="J10" s="1">
+        <v>10</v>
+      </c>
+      <c r="K10" s="1">
+        <v>12</v>
+      </c>
+      <c r="L10" s="1">
+        <v>8</v>
+      </c>
+      <c r="M10" s="1">
+        <v>11</v>
+      </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
@@ -1113,16 +1153,36 @@
       <c r="E11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
+      <c r="F11" s="3">
+        <v>7</v>
+      </c>
+      <c r="G11" s="3">
+        <v>11</v>
+      </c>
+      <c r="H11" s="3">
+        <v>6</v>
+      </c>
+      <c r="I11" s="3">
+        <v>11</v>
+      </c>
+      <c r="J11" s="3">
+        <v>11</v>
+      </c>
+      <c r="K11" s="3">
+        <v>9</v>
+      </c>
+      <c r="L11" s="3">
+        <v>11</v>
+      </c>
+      <c r="M11" s="3">
+        <v>7</v>
+      </c>
+      <c r="N11" s="3">
+        <v>8</v>
+      </c>
+      <c r="O11" s="3">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" spans="1:15" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="16">
@@ -1141,16 +1201,36 @@
       <c r="E12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
+      <c r="F12" s="3">
+        <v>11</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5</v>
+      </c>
+      <c r="H12" s="3">
+        <v>11</v>
+      </c>
+      <c r="I12" s="3">
+        <v>6</v>
+      </c>
+      <c r="J12" s="3">
+        <v>7</v>
+      </c>
+      <c r="K12" s="3">
+        <v>11</v>
+      </c>
+      <c r="L12" s="3">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
+        <v>11</v>
+      </c>
+      <c r="N12" s="3">
+        <v>11</v>
+      </c>
+      <c r="O12" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" spans="1:15" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="16">
@@ -1169,10 +1249,18 @@
       <c r="E13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="F13" s="4">
+        <v>10</v>
+      </c>
+      <c r="G13" s="4">
+        <v>12</v>
+      </c>
+      <c r="H13" s="4">
+        <v>3</v>
+      </c>
+      <c r="I13" s="4">
+        <v>11</v>
+      </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1224,12 +1312,24 @@
       <c r="E15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
+      <c r="F15" s="1">
+        <v>5</v>
+      </c>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>4</v>
+      </c>
+      <c r="I15" s="1">
+        <v>11</v>
+      </c>
+      <c r="J15" s="1">
+        <v>6</v>
+      </c>
+      <c r="K15" s="1">
+        <v>11</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -1308,12 +1408,24 @@
       <c r="E18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
+      <c r="F18" s="4">
+        <v>5</v>
+      </c>
+      <c r="G18" s="4">
+        <v>11</v>
+      </c>
+      <c r="H18" s="4">
+        <v>11</v>
+      </c>
+      <c r="I18" s="4">
+        <v>9</v>
+      </c>
+      <c r="J18" s="4">
+        <v>3</v>
+      </c>
+      <c r="K18" s="4">
+        <v>11</v>
+      </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
@@ -1336,16 +1448,36 @@
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+      <c r="F19" s="2">
+        <v>10</v>
+      </c>
+      <c r="G19" s="2">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2">
+        <v>7</v>
+      </c>
+      <c r="I19" s="2">
+        <v>11</v>
+      </c>
+      <c r="J19" s="2">
+        <v>11</v>
+      </c>
+      <c r="K19" s="2">
+        <v>4</v>
+      </c>
+      <c r="L19" s="2">
+        <v>11</v>
+      </c>
+      <c r="M19" s="2">
+        <v>4</v>
+      </c>
+      <c r="N19" s="2">
+        <v>9</v>
+      </c>
+      <c r="O19" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="20" spans="1:15" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15">

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DBC7C4-0266-4487-B607-8FC949F8C698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD7B529-7654-4B28-A1E0-3FF038CFE806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -1285,10 +1285,18 @@
       <c r="E14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="F14" s="2">
+        <v>11</v>
+      </c>
+      <c r="G14" s="2">
+        <v>2</v>
+      </c>
+      <c r="H14" s="2">
+        <v>11</v>
+      </c>
+      <c r="I14" s="2">
+        <v>2</v>
+      </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -1523,12 +1531,24 @@
       <c r="E21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="F21" s="3">
+        <v>11</v>
+      </c>
+      <c r="G21" s="3">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3">
+        <v>11</v>
+      </c>
+      <c r="I21" s="3">
+        <v>7</v>
+      </c>
+      <c r="J21" s="3">
+        <v>11</v>
+      </c>
+      <c r="K21" s="3">
+        <v>8</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
@@ -1551,14 +1571,30 @@
       <c r="E22" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
+      <c r="F22" s="3">
+        <v>11</v>
+      </c>
+      <c r="G22" s="3">
+        <v>7</v>
+      </c>
+      <c r="H22" s="3">
+        <v>7</v>
+      </c>
+      <c r="I22" s="3">
+        <v>11</v>
+      </c>
+      <c r="J22" s="3">
+        <v>9</v>
+      </c>
+      <c r="K22" s="3">
+        <v>11</v>
+      </c>
+      <c r="L22" s="3">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
+        <v>11</v>
+      </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
     </row>

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD7B529-7654-4B28-A1E0-3FF038CFE806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCD2A01-C131-4223-A2CA-B6CAF45AC2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -1360,16 +1360,36 @@
       <c r="E16" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
+      <c r="F16" s="3">
+        <v>7</v>
+      </c>
+      <c r="G16" s="3">
+        <v>11</v>
+      </c>
+      <c r="H16" s="3">
+        <v>11</v>
+      </c>
+      <c r="I16" s="3">
+        <v>9</v>
+      </c>
+      <c r="J16" s="3">
+        <v>11</v>
+      </c>
+      <c r="K16" s="3">
+        <v>5</v>
+      </c>
+      <c r="L16" s="3">
+        <v>2</v>
+      </c>
+      <c r="M16" s="3">
+        <v>11</v>
+      </c>
+      <c r="N16" s="3">
+        <v>11</v>
+      </c>
+      <c r="O16" s="3">
+        <v>8</v>
+      </c>
     </row>
     <row r="17" spans="1:15" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="16">
@@ -1388,12 +1408,24 @@
       <c r="E17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="F17" s="3">
+        <v>11</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2</v>
+      </c>
+      <c r="H17" s="3">
+        <v>11</v>
+      </c>
+      <c r="I17" s="3">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3">
+        <v>11</v>
+      </c>
+      <c r="K17" s="3">
+        <v>5</v>
+      </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
@@ -1670,10 +1702,18 @@
       <c r="E25" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="F25" s="1">
+        <v>11</v>
+      </c>
+      <c r="G25" s="1">
+        <v>7</v>
+      </c>
+      <c r="H25" s="1">
+        <v>11</v>
+      </c>
+      <c r="I25" s="1">
+        <v>8</v>
+      </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1726,12 +1766,24 @@
       <c r="E27" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
+      <c r="F27" s="3">
+        <v>13</v>
+      </c>
+      <c r="G27" s="3">
+        <v>15</v>
+      </c>
+      <c r="H27" s="3">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3">
+        <v>11</v>
+      </c>
+      <c r="J27" s="3">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
+        <v>11</v>
+      </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCD2A01-C131-4223-A2CA-B6CAF45AC2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0A483E-CF95-4CD8-951C-C72D00F6525E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -1675,12 +1675,24 @@
       <c r="E24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
+      <c r="F24" s="2">
+        <v>6</v>
+      </c>
+      <c r="G24" s="2">
+        <v>11</v>
+      </c>
+      <c r="H24" s="2">
+        <v>7</v>
+      </c>
+      <c r="I24" s="2">
+        <v>11</v>
+      </c>
+      <c r="J24" s="2">
+        <v>9</v>
+      </c>
+      <c r="K24" s="2">
+        <v>11</v>
+      </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -1738,12 +1750,24 @@
       <c r="E26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
+      <c r="F26" s="3">
+        <v>12</v>
+      </c>
+      <c r="G26" s="3">
+        <v>10</v>
+      </c>
+      <c r="H26" s="3">
+        <v>9</v>
+      </c>
+      <c r="I26" s="3">
+        <v>11</v>
+      </c>
+      <c r="J26" s="3">
+        <v>9</v>
+      </c>
+      <c r="K26" s="3">
+        <v>11</v>
+      </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
@@ -1806,14 +1830,30 @@
       <c r="E28" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
+      <c r="F28" s="4">
+        <v>8</v>
+      </c>
+      <c r="G28" s="4">
+        <v>11</v>
+      </c>
+      <c r="H28" s="4">
+        <v>11</v>
+      </c>
+      <c r="I28" s="4">
+        <v>9</v>
+      </c>
+      <c r="J28" s="4">
+        <v>11</v>
+      </c>
+      <c r="K28" s="4">
+        <v>9</v>
+      </c>
+      <c r="L28" s="4">
+        <v>11</v>
+      </c>
+      <c r="M28" s="4">
+        <v>7</v>
+      </c>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
     </row>
@@ -1833,12 +1873,24 @@
       <c r="E29" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
+      <c r="F29" s="1">
+        <v>4</v>
+      </c>
+      <c r="G29" s="1">
+        <v>11</v>
+      </c>
+      <c r="H29" s="1">
+        <v>12</v>
+      </c>
+      <c r="I29" s="1">
+        <v>10</v>
+      </c>
+      <c r="J29" s="1">
+        <v>6</v>
+      </c>
+      <c r="K29" s="1">
+        <v>11</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -1889,16 +1941,36 @@
       <c r="E31" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
+      <c r="F31" s="3">
+        <v>5</v>
+      </c>
+      <c r="G31" s="3">
+        <v>11</v>
+      </c>
+      <c r="H31" s="3">
+        <v>11</v>
+      </c>
+      <c r="I31" s="3">
+        <v>5</v>
+      </c>
+      <c r="J31" s="3">
+        <v>11</v>
+      </c>
+      <c r="K31" s="3">
+        <v>7</v>
+      </c>
+      <c r="L31" s="3">
+        <v>10</v>
+      </c>
+      <c r="M31" s="3">
+        <v>12</v>
+      </c>
+      <c r="N31" s="3">
+        <v>11</v>
+      </c>
+      <c r="O31" s="3">
+        <v>9</v>
+      </c>
     </row>
     <row r="32" spans="1:15" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="16">
@@ -1917,12 +1989,24 @@
       <c r="E32" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
+      <c r="F32" s="4">
+        <v>15</v>
+      </c>
+      <c r="G32" s="4">
+        <v>13</v>
+      </c>
+      <c r="H32" s="4">
+        <v>11</v>
+      </c>
+      <c r="I32" s="4">
+        <v>8</v>
+      </c>
+      <c r="J32" s="4">
+        <v>12</v>
+      </c>
+      <c r="K32" s="4">
+        <v>10</v>
+      </c>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0A483E-CF95-4CD8-951C-C72D00F6525E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD4B406-81F4-4371-80A2-AC83B13A4605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1647,12 +1647,24 @@
       <c r="E23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
+      <c r="F23" s="4">
+        <v>3</v>
+      </c>
+      <c r="G23" s="4">
+        <v>11</v>
+      </c>
+      <c r="H23" s="4">
+        <v>9</v>
+      </c>
+      <c r="I23" s="4">
+        <v>11</v>
+      </c>
+      <c r="J23" s="4">
+        <v>10</v>
+      </c>
+      <c r="K23" s="4">
+        <v>12</v>
+      </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
@@ -2029,12 +2041,24 @@
       <c r="E33" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
+      <c r="F33" s="2">
+        <v>11</v>
+      </c>
+      <c r="G33" s="2">
+        <v>6</v>
+      </c>
+      <c r="H33" s="2">
+        <v>11</v>
+      </c>
+      <c r="I33" s="2">
+        <v>8</v>
+      </c>
+      <c r="J33" s="2">
+        <v>11</v>
+      </c>
+      <c r="K33" s="2">
+        <v>2</v>
+      </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -2056,12 +2080,24 @@
       <c r="E34" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
+      <c r="F34" s="1">
+        <v>11</v>
+      </c>
+      <c r="G34" s="1">
+        <v>4</v>
+      </c>
+      <c r="H34" s="1">
+        <v>12</v>
+      </c>
+      <c r="I34" s="1">
+        <v>14</v>
+      </c>
+      <c r="J34" s="1">
+        <v>11</v>
+      </c>
+      <c r="K34" s="1">
+        <v>4</v>
+      </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -2084,10 +2120,18 @@
       <c r="E35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="F35" s="3">
+        <v>11</v>
+      </c>
+      <c r="G35" s="3">
+        <v>2</v>
+      </c>
+      <c r="H35" s="3">
+        <v>11</v>
+      </c>
+      <c r="I35" s="3">
+        <v>5</v>
+      </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
@@ -2112,16 +2156,36 @@
       <c r="E36" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
+      <c r="F36" s="3">
+        <v>11</v>
+      </c>
+      <c r="G36" s="3">
+        <v>8</v>
+      </c>
+      <c r="H36" s="3">
+        <v>13</v>
+      </c>
+      <c r="I36" s="3">
+        <v>15</v>
+      </c>
+      <c r="J36" s="3">
+        <v>8</v>
+      </c>
+      <c r="K36" s="3">
+        <v>11</v>
+      </c>
+      <c r="L36" s="3">
+        <v>11</v>
+      </c>
+      <c r="M36" s="3">
+        <v>9</v>
+      </c>
+      <c r="N36" s="3">
+        <v>4</v>
+      </c>
+      <c r="O36" s="3">
+        <v>11</v>
+      </c>
     </row>
     <row r="37" spans="1:15" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="16">
@@ -2140,16 +2204,36 @@
       <c r="E37" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
+      <c r="F37" s="4">
+        <v>11</v>
+      </c>
+      <c r="G37" s="4">
+        <v>9</v>
+      </c>
+      <c r="H37" s="4">
+        <v>8</v>
+      </c>
+      <c r="I37" s="4">
+        <v>11</v>
+      </c>
+      <c r="J37" s="4">
+        <v>12</v>
+      </c>
+      <c r="K37" s="4">
+        <v>14</v>
+      </c>
+      <c r="L37" s="4">
+        <v>11</v>
+      </c>
+      <c r="M37" s="4">
+        <v>8</v>
+      </c>
+      <c r="N37" s="4">
+        <v>11</v>
+      </c>
+      <c r="O37" s="4">
+        <v>9</v>
+      </c>
     </row>
     <row r="38" spans="1:15" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="17">
@@ -2168,12 +2252,24 @@
       <c r="E38" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
+      <c r="F38" s="2">
+        <v>11</v>
+      </c>
+      <c r="G38" s="2">
+        <v>5</v>
+      </c>
+      <c r="H38" s="2">
+        <v>11</v>
+      </c>
+      <c r="I38" s="2">
+        <v>7</v>
+      </c>
+      <c r="J38" s="2">
+        <v>11</v>
+      </c>
+      <c r="K38" s="2">
+        <v>3</v>
+      </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD4B406-81F4-4371-80A2-AC83B13A4605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD2FEF9-7542-47A3-9780-F45403DAA48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1925,10 +1925,18 @@
       <c r="E30" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+      <c r="F30" s="3">
+        <v>11</v>
+      </c>
+      <c r="G30" s="3">
+        <v>6</v>
+      </c>
+      <c r="H30" s="3">
+        <v>11</v>
+      </c>
+      <c r="I30" s="3">
+        <v>3</v>
+      </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
@@ -2291,10 +2299,18 @@
       <c r="E39" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
+      <c r="F39" s="1">
+        <v>11</v>
+      </c>
+      <c r="G39" s="1">
+        <v>13</v>
+      </c>
+      <c r="H39" s="1">
+        <v>8</v>
+      </c>
+      <c r="I39" s="1">
+        <v>11</v>
+      </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -2319,16 +2335,36 @@
       <c r="E40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
+      <c r="F40" s="3">
+        <v>9</v>
+      </c>
+      <c r="G40" s="3">
+        <v>11</v>
+      </c>
+      <c r="H40" s="3">
+        <v>7</v>
+      </c>
+      <c r="I40" s="3">
+        <v>11</v>
+      </c>
+      <c r="J40" s="3">
+        <v>12</v>
+      </c>
+      <c r="K40" s="3">
+        <v>10</v>
+      </c>
+      <c r="L40" s="3">
+        <v>11</v>
+      </c>
+      <c r="M40" s="3">
+        <v>6</v>
+      </c>
+      <c r="N40" s="3">
+        <v>11</v>
+      </c>
+      <c r="O40" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="41" spans="1:15" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="16">
@@ -2403,16 +2439,36 @@
       <c r="E43" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="F43" s="2">
+        <v>5</v>
+      </c>
+      <c r="G43" s="2">
+        <v>11</v>
+      </c>
+      <c r="H43" s="2">
+        <v>12</v>
+      </c>
+      <c r="I43" s="2">
+        <v>10</v>
+      </c>
+      <c r="J43" s="2">
+        <v>11</v>
+      </c>
+      <c r="K43" s="2">
+        <v>8</v>
+      </c>
+      <c r="L43" s="2">
+        <v>6</v>
+      </c>
+      <c r="M43" s="2">
+        <v>11</v>
+      </c>
+      <c r="N43" s="2">
+        <v>11</v>
+      </c>
+      <c r="O43" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="44" spans="1:15" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="15">

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD2FEF9-7542-47A3-9780-F45403DAA48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108F0587-F3FB-4412-8BC6-BE00E4C6BCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -2411,12 +2411,24 @@
       <c r="E42" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
+      <c r="F42" s="4">
+        <v>11</v>
+      </c>
+      <c r="G42" s="4">
+        <v>3</v>
+      </c>
+      <c r="H42" s="4">
+        <v>11</v>
+      </c>
+      <c r="I42" s="4">
+        <v>4</v>
+      </c>
+      <c r="J42" s="4">
+        <v>11</v>
+      </c>
+      <c r="K42" s="4">
+        <v>6</v>
+      </c>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
@@ -2542,12 +2554,24 @@
       <c r="E46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
+      <c r="F46" s="3">
+        <v>11</v>
+      </c>
+      <c r="G46" s="3">
+        <v>7</v>
+      </c>
+      <c r="H46" s="3">
+        <v>7</v>
+      </c>
+      <c r="I46" s="3">
+        <v>11</v>
+      </c>
+      <c r="J46" s="3">
+        <v>11</v>
+      </c>
+      <c r="K46" s="3">
+        <v>4</v>
+      </c>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
@@ -2570,10 +2594,18 @@
       <c r="E47" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
+      <c r="F47" s="4">
+        <v>3</v>
+      </c>
+      <c r="G47" s="4">
+        <v>11</v>
+      </c>
+      <c r="H47" s="4">
+        <v>4</v>
+      </c>
+      <c r="I47" s="4">
+        <v>11</v>
+      </c>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2598,12 +2630,24 @@
       <c r="E48" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
+      <c r="F48" s="2">
+        <v>7</v>
+      </c>
+      <c r="G48" s="2">
+        <v>11</v>
+      </c>
+      <c r="H48" s="2">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2">
+        <v>11</v>
+      </c>
+      <c r="J48" s="2">
+        <v>8</v>
+      </c>
+      <c r="K48" s="2">
+        <v>11</v>
+      </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -2653,16 +2697,36 @@
       <c r="E50" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
+      <c r="F50" s="3">
+        <v>10</v>
+      </c>
+      <c r="G50" s="3">
+        <v>12</v>
+      </c>
+      <c r="H50" s="3">
+        <v>11</v>
+      </c>
+      <c r="I50" s="3">
+        <v>8</v>
+      </c>
+      <c r="J50" s="3">
+        <v>7</v>
+      </c>
+      <c r="K50" s="3">
+        <v>11</v>
+      </c>
+      <c r="L50" s="3">
+        <v>11</v>
+      </c>
+      <c r="M50" s="3">
+        <v>6</v>
+      </c>
+      <c r="N50" s="3">
+        <v>15</v>
+      </c>
+      <c r="O50" s="3">
+        <v>13</v>
+      </c>
     </row>
     <row r="51" spans="1:15" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="16">

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108F0587-F3FB-4412-8BC6-BE00E4C6BCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4798288-4864-4BFF-9BC2-363017FC1E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -2669,12 +2669,24 @@
       <c r="E49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
+      <c r="F49" s="1">
+        <v>11</v>
+      </c>
+      <c r="G49" s="1">
+        <v>13</v>
+      </c>
+      <c r="H49" s="1">
+        <v>8</v>
+      </c>
+      <c r="I49" s="1">
+        <v>11</v>
+      </c>
+      <c r="J49" s="1">
+        <v>10</v>
+      </c>
+      <c r="K49" s="1">
+        <v>12</v>
+      </c>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
@@ -2828,14 +2840,30 @@
       <c r="E54" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
+      <c r="F54" s="1">
+        <v>6</v>
+      </c>
+      <c r="G54" s="1">
+        <v>11</v>
+      </c>
+      <c r="H54" s="1">
+        <v>11</v>
+      </c>
+      <c r="I54" s="1">
+        <v>1</v>
+      </c>
+      <c r="J54" s="1">
+        <v>11</v>
+      </c>
+      <c r="K54" s="1">
+        <v>5</v>
+      </c>
+      <c r="L54" s="1">
+        <v>11</v>
+      </c>
+      <c r="M54" s="1">
+        <v>6</v>
+      </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
     </row>
@@ -2884,10 +2912,18 @@
       <c r="E56" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
+      <c r="F56" s="3">
+        <v>11</v>
+      </c>
+      <c r="G56" s="3">
+        <v>9</v>
+      </c>
+      <c r="H56" s="3">
+        <v>11</v>
+      </c>
+      <c r="I56" s="3">
+        <v>3</v>
+      </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
@@ -2912,10 +2948,18 @@
       <c r="E57" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
+      <c r="F57" s="4">
+        <v>11</v>
+      </c>
+      <c r="G57" s="4">
+        <v>0</v>
+      </c>
+      <c r="H57" s="4">
+        <v>11</v>
+      </c>
+      <c r="I57" s="4">
+        <v>0</v>
+      </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
@@ -2940,16 +2984,36 @@
       <c r="E58" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+      <c r="F58" s="2">
+        <v>11</v>
+      </c>
+      <c r="G58" s="2">
+        <v>7</v>
+      </c>
+      <c r="H58" s="2">
+        <v>12</v>
+      </c>
+      <c r="I58" s="2">
+        <v>10</v>
+      </c>
+      <c r="J58" s="2">
+        <v>11</v>
+      </c>
+      <c r="K58" s="2">
+        <v>13</v>
+      </c>
+      <c r="L58" s="2">
+        <v>9</v>
+      </c>
+      <c r="M58" s="2">
+        <v>11</v>
+      </c>
+      <c r="N58" s="2">
+        <v>6</v>
+      </c>
+      <c r="O58" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="59" spans="1:15" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="15">
@@ -2967,12 +3031,24 @@
       <c r="E59" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
+      <c r="F59" s="1">
+        <v>11</v>
+      </c>
+      <c r="G59" s="1">
+        <v>9</v>
+      </c>
+      <c r="H59" s="1">
+        <v>11</v>
+      </c>
+      <c r="I59" s="1">
+        <v>9</v>
+      </c>
+      <c r="J59" s="1">
+        <v>11</v>
+      </c>
+      <c r="K59" s="1">
+        <v>8</v>
+      </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
@@ -2995,12 +3071,24 @@
       <c r="E60" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
+      <c r="F60" s="3">
+        <v>11</v>
+      </c>
+      <c r="G60" s="3">
+        <v>6</v>
+      </c>
+      <c r="H60" s="3">
+        <v>13</v>
+      </c>
+      <c r="I60" s="3">
+        <v>11</v>
+      </c>
+      <c r="J60" s="3">
+        <v>11</v>
+      </c>
+      <c r="K60" s="3">
+        <v>7</v>
+      </c>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
@@ -3023,10 +3111,18 @@
       <c r="E61" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
+      <c r="F61" s="3">
+        <v>10</v>
+      </c>
+      <c r="G61" s="3">
+        <v>12</v>
+      </c>
+      <c r="H61" s="3">
+        <v>7</v>
+      </c>
+      <c r="I61" s="3">
+        <v>11</v>
+      </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
@@ -3051,14 +3147,30 @@
       <c r="E62" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
+      <c r="F62" s="4">
+        <v>8</v>
+      </c>
+      <c r="G62" s="4">
+        <v>11</v>
+      </c>
+      <c r="H62" s="4">
+        <v>12</v>
+      </c>
+      <c r="I62" s="4">
+        <v>10</v>
+      </c>
+      <c r="J62" s="4">
+        <v>11</v>
+      </c>
+      <c r="K62" s="4">
+        <v>5</v>
+      </c>
+      <c r="L62" s="4">
+        <v>11</v>
+      </c>
+      <c r="M62" s="4">
+        <v>3</v>
+      </c>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
     </row>

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4798288-4864-4BFF-9BC2-363017FC1E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A16CDE3-F32D-4A74-A747-B4A91BF54B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -3274,12 +3274,24 @@
       <c r="E66" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
+      <c r="F66" s="4">
+        <v>11</v>
+      </c>
+      <c r="G66" s="4">
+        <v>6</v>
+      </c>
+      <c r="H66" s="4">
+        <v>11</v>
+      </c>
+      <c r="I66" s="4">
+        <v>6</v>
+      </c>
+      <c r="J66" s="4">
+        <v>11</v>
+      </c>
+      <c r="K66" s="4">
+        <v>3</v>
+      </c>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
@@ -3302,10 +3314,18 @@
       <c r="E67" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
+      <c r="F67" s="2">
+        <v>11</v>
+      </c>
+      <c r="G67" s="2">
+        <v>6</v>
+      </c>
+      <c r="H67" s="2">
+        <v>11</v>
+      </c>
+      <c r="I67" s="2">
+        <v>7</v>
+      </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
@@ -3524,16 +3544,36 @@
       <c r="E75" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
-      <c r="O75" s="3"/>
+      <c r="F75" s="3">
+        <v>11</v>
+      </c>
+      <c r="G75" s="3">
+        <v>5</v>
+      </c>
+      <c r="H75" s="3">
+        <v>10</v>
+      </c>
+      <c r="I75" s="3">
+        <v>12</v>
+      </c>
+      <c r="J75" s="3">
+        <v>12</v>
+      </c>
+      <c r="K75" s="3">
+        <v>10</v>
+      </c>
+      <c r="L75" s="3">
+        <v>5</v>
+      </c>
+      <c r="M75" s="3">
+        <v>11</v>
+      </c>
+      <c r="N75" s="3">
+        <v>11</v>
+      </c>
+      <c r="O75" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="76" spans="1:15" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="17">

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A16CDE3-F32D-4A74-A747-B4A91BF54B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7159DAFF-05DC-46DB-89BA-AE664EC77F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -2498,16 +2498,36 @@
       <c r="E44" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
+      <c r="F44" s="1">
+        <v>12</v>
+      </c>
+      <c r="G44" s="1">
+        <v>10</v>
+      </c>
+      <c r="H44" s="1">
+        <v>9</v>
+      </c>
+      <c r="I44" s="1">
+        <v>11</v>
+      </c>
+      <c r="J44" s="1">
+        <v>11</v>
+      </c>
+      <c r="K44" s="1">
+        <v>6</v>
+      </c>
+      <c r="L44" s="1">
+        <v>11</v>
+      </c>
+      <c r="M44" s="1">
+        <v>13</v>
+      </c>
+      <c r="N44" s="1">
+        <v>3</v>
+      </c>
+      <c r="O44" s="1">
+        <v>11</v>
+      </c>
     </row>
     <row r="45" spans="1:15" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="16">
@@ -2785,12 +2805,24 @@
       <c r="E52" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
+      <c r="F52" s="4">
+        <v>11</v>
+      </c>
+      <c r="G52" s="4">
+        <v>9</v>
+      </c>
+      <c r="H52" s="4">
+        <v>8</v>
+      </c>
+      <c r="I52" s="4">
+        <v>11</v>
+      </c>
+      <c r="J52" s="4">
+        <v>12</v>
+      </c>
+      <c r="K52" s="4">
+        <v>10</v>
+      </c>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
@@ -2884,14 +2916,30 @@
       <c r="E55" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
+      <c r="F55" s="3">
+        <v>11</v>
+      </c>
+      <c r="G55" s="3">
+        <v>6</v>
+      </c>
+      <c r="H55" s="3">
+        <v>11</v>
+      </c>
+      <c r="I55" s="3">
+        <v>8</v>
+      </c>
+      <c r="J55" s="3">
+        <v>8</v>
+      </c>
+      <c r="K55" s="3">
+        <v>11</v>
+      </c>
+      <c r="L55" s="3">
+        <v>11</v>
+      </c>
+      <c r="M55" s="3">
+        <v>8</v>
+      </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
     </row>
@@ -3246,14 +3294,30 @@
       <c r="E65" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
+      <c r="F65" s="3">
+        <v>13</v>
+      </c>
+      <c r="G65" s="3">
+        <v>11</v>
+      </c>
+      <c r="H65" s="3">
+        <v>1</v>
+      </c>
+      <c r="I65" s="3">
+        <v>11</v>
+      </c>
+      <c r="J65" s="3">
+        <v>7</v>
+      </c>
+      <c r="K65" s="3">
+        <v>11</v>
+      </c>
+      <c r="L65" s="3">
+        <v>4</v>
+      </c>
+      <c r="M65" s="3">
+        <v>11</v>
+      </c>
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
     </row>
@@ -3405,12 +3469,24 @@
       <c r="E70" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
+      <c r="F70" s="3">
+        <v>5</v>
+      </c>
+      <c r="G70" s="3">
+        <v>11</v>
+      </c>
+      <c r="H70" s="3">
+        <v>5</v>
+      </c>
+      <c r="I70" s="3">
+        <v>11</v>
+      </c>
+      <c r="J70" s="3">
+        <v>13</v>
+      </c>
+      <c r="K70" s="3">
+        <v>15</v>
+      </c>
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
@@ -3433,14 +3509,30 @@
       <c r="E71" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
+      <c r="F71" s="4">
+        <v>3</v>
+      </c>
+      <c r="G71" s="4">
+        <v>11</v>
+      </c>
+      <c r="H71" s="4">
+        <v>11</v>
+      </c>
+      <c r="I71" s="4">
+        <v>5</v>
+      </c>
+      <c r="J71" s="4">
+        <v>7</v>
+      </c>
+      <c r="K71" s="4">
+        <v>11</v>
+      </c>
+      <c r="L71" s="4">
+        <v>5</v>
+      </c>
+      <c r="M71" s="4">
+        <v>11</v>
+      </c>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
     </row>
@@ -3488,10 +3580,18 @@
       <c r="E73" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
+      <c r="F73" s="1">
+        <v>10</v>
+      </c>
+      <c r="G73" s="1">
+        <v>12</v>
+      </c>
+      <c r="H73" s="1">
+        <v>9</v>
+      </c>
+      <c r="I73" s="1">
+        <v>11</v>
+      </c>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7159DAFF-05DC-46DB-89BA-AE664EC77F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4070536-DC37-4A2F-879D-633B64B33481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -2383,12 +2383,24 @@
       <c r="E41" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
+      <c r="F41" s="3">
+        <v>4</v>
+      </c>
+      <c r="G41" s="3">
+        <v>11</v>
+      </c>
+      <c r="H41" s="3">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3">
+        <v>11</v>
+      </c>
+      <c r="J41" s="3">
+        <v>7</v>
+      </c>
+      <c r="K41" s="3">
+        <v>11</v>
+      </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
@@ -2777,10 +2789,18 @@
       <c r="E51" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
+      <c r="F51" s="3">
+        <v>11</v>
+      </c>
+      <c r="G51" s="3">
+        <v>3</v>
+      </c>
+      <c r="H51" s="3">
+        <v>11</v>
+      </c>
+      <c r="I51" s="3">
+        <v>7</v>
+      </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
@@ -3441,14 +3461,30 @@
       <c r="E69" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
+      <c r="F69" s="3">
+        <v>6</v>
+      </c>
+      <c r="G69" s="3">
+        <v>11</v>
+      </c>
+      <c r="H69" s="3">
+        <v>11</v>
+      </c>
+      <c r="I69" s="3">
+        <v>9</v>
+      </c>
+      <c r="J69" s="3">
+        <v>7</v>
+      </c>
+      <c r="K69" s="3">
+        <v>11</v>
+      </c>
+      <c r="L69" s="3">
+        <v>6</v>
+      </c>
+      <c r="M69" s="3">
+        <v>11</v>
+      </c>
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
     </row>
@@ -3616,14 +3652,30 @@
       <c r="E74" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
+      <c r="F74" s="3">
+        <v>11</v>
+      </c>
+      <c r="G74" s="3">
+        <v>8</v>
+      </c>
+      <c r="H74" s="3">
+        <v>8</v>
+      </c>
+      <c r="I74" s="3">
+        <v>11</v>
+      </c>
+      <c r="J74" s="3">
+        <v>9</v>
+      </c>
+      <c r="K74" s="3">
+        <v>11</v>
+      </c>
+      <c r="L74" s="3">
+        <v>8</v>
+      </c>
+      <c r="M74" s="3">
+        <v>11</v>
+      </c>
       <c r="N74" s="3"/>
       <c r="O74" s="3"/>
     </row>

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4070536-DC37-4A2F-879D-633B64B33481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEDF9103-F2D7-40C5-A2D7-E78BEAFCA006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -3771,10 +3771,18 @@
       <c r="E77" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
+      <c r="F77" s="1">
+        <v>11</v>
+      </c>
+      <c r="G77" s="1">
+        <v>3</v>
+      </c>
+      <c r="H77" s="1">
+        <v>11</v>
+      </c>
+      <c r="I77" s="1">
+        <v>1</v>
+      </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
@@ -3827,12 +3835,24 @@
       <c r="E79" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
+      <c r="F79" s="3">
+        <v>11</v>
+      </c>
+      <c r="G79" s="3">
+        <v>6</v>
+      </c>
+      <c r="H79" s="3">
+        <v>11</v>
+      </c>
+      <c r="I79" s="3">
+        <v>4</v>
+      </c>
+      <c r="J79" s="3">
+        <v>11</v>
+      </c>
+      <c r="K79" s="3">
+        <v>4</v>
+      </c>
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
@@ -3855,12 +3875,24 @@
       <c r="E80" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
+      <c r="F80" s="4">
+        <v>11</v>
+      </c>
+      <c r="G80" s="4">
+        <v>2</v>
+      </c>
+      <c r="H80" s="4">
+        <v>11</v>
+      </c>
+      <c r="I80" s="4">
+        <v>8</v>
+      </c>
+      <c r="J80" s="4">
+        <v>11</v>
+      </c>
+      <c r="K80" s="4">
+        <v>4</v>
+      </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
       <c r="N80" s="4"/>
@@ -3883,10 +3915,18 @@
       <c r="E81" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
+      <c r="F81" s="2">
+        <v>11</v>
+      </c>
+      <c r="G81" s="2">
+        <v>7</v>
+      </c>
+      <c r="H81" s="2">
+        <v>11</v>
+      </c>
+      <c r="I81" s="2">
+        <v>2</v>
+      </c>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>

--- a/RESULTADOS T7.xlsx
+++ b/RESULTADOS T7.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEDF9103-F2D7-40C5-A2D7-E78BEAFCA006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20ABC095-CEBE-48CB-9E05-03A4B4C4DA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -1535,12 +1535,24 @@
       <c r="E20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
+      <c r="F20" s="1">
+        <v>11</v>
+      </c>
+      <c r="G20" s="1">
+        <v>6</v>
+      </c>
+      <c r="H20" s="1">
+        <v>12</v>
+      </c>
+      <c r="I20" s="1">
+        <v>10</v>
+      </c>
+      <c r="J20" s="1">
+        <v>11</v>
+      </c>
+      <c r="K20" s="1">
+        <v>6</v>
+      </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -3286,14 +3298,30 @@
       <c r="E64" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
+      <c r="F64" s="3">
+        <v>12</v>
+      </c>
+      <c r="G64" s="3">
+        <v>10</v>
+      </c>
+      <c r="H64" s="3">
+        <v>9</v>
+      </c>
+      <c r="I64" s="3">
+        <v>11</v>
+      </c>
+      <c r="J64" s="3">
+        <v>11</v>
+      </c>
+      <c r="K64" s="3">
+        <v>4</v>
+      </c>
+      <c r="L64" s="3">
+        <v>11</v>
+      </c>
+      <c r="M64" s="3">
+        <v>2</v>
+      </c>
       <c r="N64" s="3"/>
       <c r="O64" s="3"/>
     </row>
@@ -3433,10 +3461,18 @@
       <c r="E68" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
+      <c r="F68" s="1">
+        <v>6</v>
+      </c>
+      <c r="G68" s="1">
+        <v>11</v>
+      </c>
+      <c r="H68" s="1">
+        <v>3</v>
+      </c>
+      <c r="I68" s="1">
+        <v>11</v>
+      </c>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -3744,10 +3780,18 @@
       <c r="E76" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
+      <c r="F76" s="2">
+        <v>11</v>
+      </c>
+      <c r="G76" s="2">
+        <v>9</v>
+      </c>
+      <c r="H76" s="2">
+        <v>11</v>
+      </c>
+      <c r="I76" s="2">
+        <v>9</v>
+      </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
@@ -4034,16 +4078,36 @@
       <c r="E85" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="4"/>
-      <c r="M85" s="4"/>
-      <c r="N85" s="4"/>
-      <c r="O85" s="4"/>
+      <c r="F85" s="4">
+        <v>11</v>
+      </c>
+      <c r="G85" s="4">
+        <v>9</v>
+      </c>
+      <c r="H85" s="4">
+        <v>3</v>
+      </c>
+      <c r="I85" s="4">
+        <v>11</v>
+      </c>
+      <c r="J85" s="4">
+        <v>10</v>
+      </c>
+      <c r="K85" s="4">
+        <v>12</v>
+      </c>
+      <c r="L85" s="4">
+        <v>11</v>
+      </c>
+      <c r="M85" s="4">
+        <v>8</v>
+      </c>
+      <c r="N85" s="4">
+        <v>6</v>
+      </c>
+      <c r="O85" s="4">
+        <v>11</v>
+      </c>
     </row>
     <row r="86" spans="1:15" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="17">
@@ -4117,10 +4181,18 @@
       <c r="E88" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
+      <c r="F88" s="3">
+        <v>11</v>
+      </c>
+      <c r="G88" s="3">
+        <v>6</v>
+      </c>
+      <c r="H88" s="3">
+        <v>11</v>
+      </c>
+      <c r="I88" s="3">
+        <v>4</v>
+      </c>
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
       <c r="L88" s="3"/>
@@ -4201,16 +4273,36 @@
       <c r="E91" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
-      <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+      <c r="F91" s="2">
+        <v>11</v>
+      </c>
+      <c r="G91" s="2">
+        <v>8</v>
+      </c>
+      <c r="H91" s="2">
+        <v>5</v>
+      </c>
+      <c r="I91" s="2">
+        <v>11</v>
+      </c>
+      <c r="J91" s="2">
+        <v>11</v>
+      </c>
+      <c r="K91" s="2">
+        <v>8</v>
+      </c>
+      <c r="L91" s="2">
+        <v>6</v>
+      </c>
+      <c r="M91" s="2">
+        <v>11</v>
+      </c>
+      <c r="N91" s="2">
+        <v>6</v>
+      </c>
+      <c r="O91" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="92" spans="1:15" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="15">
